--- a/performance_report.xlsx
+++ b/performance_report.xlsx
@@ -600,28 +600,28 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.399</v>
+        <v>1.693</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.158</v>
+        <v>1.87</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3.087</v>
+        <v>4.102</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.544</v>
+        <v>5.154</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.781</v>
+        <v>4.804</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.029</v>
+        <v>4.915</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25.22</v>
+        <v>5.82</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2973.6</v>
+        <v>2795.5</v>
       </c>
     </row>
     <row r="3">
@@ -629,28 +629,28 @@
         <v>50</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2.445</v>
+        <v>1.704</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.502</v>
+        <v>1.909</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3.188</v>
+        <v>4.297</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3.371</v>
+        <v>4.671</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.49</v>
+        <v>4.636</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>3.839</v>
+        <v>4.835</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>13.7</v>
+        <v>4.08</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2965.9</v>
+        <v>2808.6</v>
       </c>
     </row>
     <row r="4">
@@ -658,28 +658,28 @@
         <v>100</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.937</v>
+        <v>1.59</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2.202</v>
+        <v>1.626</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2.459</v>
+        <v>3.741</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.739</v>
+        <v>4.269</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.939</v>
+        <v>4.046</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3.183</v>
+        <v>5.055</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12.7</v>
+        <v>10.76</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2862.2</v>
+        <v>2823.4</v>
       </c>
     </row>
     <row r="5">
@@ -687,28 +687,28 @@
         <v>200</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1.734</v>
+        <v>2.415</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2.054</v>
+        <v>3.754</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.551</v>
+        <v>4.382</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3.021</v>
+        <v>4.645</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.972</v>
+        <v>4.292</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>3.473</v>
+        <v>4.781</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15.08</v>
+        <v>4.01</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2785.1</v>
+        <v>2877.1</v>
       </c>
     </row>
     <row r="6">
@@ -716,28 +716,28 @@
         <v>500</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.689</v>
+        <v>1.522</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.72</v>
+        <v>1.713</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.554</v>
+        <v>3.695</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.617</v>
+        <v>4.388</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.781</v>
+        <v>3.983</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4.148</v>
+        <v>4.726</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.32</v>
+        <v>5.59</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2737.4</v>
+        <v>2903.3</v>
       </c>
     </row>
   </sheetData>
@@ -829,31 +829,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>4.158</v>
+        <v>1.87</v>
       </c>
       <c r="C2" t="n">
-        <v>3.544</v>
+        <v>4.54</v>
       </c>
       <c r="D2" t="n">
-        <v>3.739</v>
+        <v>4.699</v>
       </c>
       <c r="E2" t="n">
-        <v>40.6</v>
+        <v>2.7</v>
       </c>
       <c r="F2" t="n">
-        <v>47.4</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>18.4</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2976.3</v>
+        <v>2764.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2935.5</v>
+        <v>2773.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2934.1</v>
+        <v>2779.6</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -864,31 +864,31 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>3.093</v>
+        <v>1.68</v>
       </c>
       <c r="C3" t="n">
-        <v>2.912</v>
+        <v>2.612</v>
       </c>
       <c r="D3" t="n">
-        <v>3.574</v>
+        <v>4.915</v>
       </c>
       <c r="E3" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="F3" t="n">
-        <v>27.8</v>
+        <v>29.9</v>
       </c>
       <c r="G3" t="n">
-        <v>21.4</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2946.8</v>
+        <v>2781</v>
       </c>
       <c r="I3" t="n">
-        <v>2988.3</v>
+        <v>2809.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2992.8</v>
+        <v>2811.9</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -899,31 +899,31 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>2.945</v>
+        <v>1.53</v>
       </c>
       <c r="C4" t="n">
-        <v>2.805</v>
+        <v>5.154</v>
       </c>
       <c r="D4" t="n">
-        <v>4.029</v>
+        <v>4.797</v>
       </c>
       <c r="E4" t="n">
-        <v>19.6</v>
+        <v>2.2</v>
       </c>
       <c r="F4" t="n">
-        <v>24.5</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2996.9</v>
+        <v>2813.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2995.2</v>
+        <v>2813.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2996.2</v>
+        <v>2812.7</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -934,31 +934,31 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2.502</v>
+        <v>1.661</v>
       </c>
       <c r="C5" t="n">
-        <v>3.264</v>
+        <v>4.671</v>
       </c>
       <c r="D5" t="n">
-        <v>3.839</v>
+        <v>4.835</v>
       </c>
       <c r="E5" t="n">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2982.6</v>
+        <v>2809.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2978.5</v>
+        <v>2810.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2976.3</v>
+        <v>2809.6</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -969,31 +969,31 @@
         <v>50</v>
       </c>
       <c r="B6" t="n">
-        <v>2.46</v>
+        <v>1.543</v>
       </c>
       <c r="C6" t="n">
-        <v>3.371</v>
+        <v>4.412</v>
       </c>
       <c r="D6" t="n">
-        <v>3.64</v>
+        <v>4.553</v>
       </c>
       <c r="E6" t="n">
-        <v>20.8</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>21.5</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>10.1</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2965.1</v>
+        <v>2808.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2954.8</v>
+        <v>2808.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2964.9</v>
+        <v>2805.7</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -1004,31 +1004,31 @@
         <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>2.374</v>
+        <v>1.909</v>
       </c>
       <c r="C7" t="n">
-        <v>2.93</v>
+        <v>3.808</v>
       </c>
       <c r="D7" t="n">
-        <v>2.991</v>
+        <v>4.52</v>
       </c>
       <c r="E7" t="n">
-        <v>14.8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2957.1</v>
+        <v>2804.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2956.5</v>
+        <v>2810.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2956.9</v>
+        <v>2810.3</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -1039,31 +1039,31 @@
         <v>100</v>
       </c>
       <c r="B8" t="n">
-        <v>2.202</v>
+        <v>1.626</v>
       </c>
       <c r="C8" t="n">
-        <v>2.451</v>
+        <v>2.911</v>
       </c>
       <c r="D8" t="n">
-        <v>2.816</v>
+        <v>2.73</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="F8" t="n">
-        <v>6.5</v>
+        <v>12.9</v>
       </c>
       <c r="G8" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2912.1</v>
+        <v>2804</v>
       </c>
       <c r="I8" t="n">
-        <v>2914.7</v>
+        <v>2768.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2915.7</v>
+        <v>2757.3</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -1074,31 +1074,31 @@
         <v>100</v>
       </c>
       <c r="B9" t="n">
-        <v>1.782</v>
+        <v>1.527</v>
       </c>
       <c r="C9" t="n">
-        <v>2.739</v>
+        <v>4.044</v>
       </c>
       <c r="D9" t="n">
-        <v>2.818</v>
+        <v>5.055</v>
       </c>
       <c r="E9" t="n">
-        <v>10.3</v>
+        <v>23.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7.3</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2854.1</v>
+        <v>2786.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2855.7</v>
+        <v>2859.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2845.7</v>
+        <v>2859.4</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -1109,31 +1109,31 @@
         <v>100</v>
       </c>
       <c r="B10" t="n">
-        <v>1.828</v>
+        <v>1.617</v>
       </c>
       <c r="C10" t="n">
-        <v>2.188</v>
+        <v>4.269</v>
       </c>
       <c r="D10" t="n">
-        <v>3.183</v>
+        <v>4.354</v>
       </c>
       <c r="E10" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2818.7</v>
+        <v>2857.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2821.5</v>
+        <v>2858.6</v>
       </c>
       <c r="J10" t="n">
-        <v>2821.6</v>
+        <v>2858.9</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1144,31 +1144,31 @@
         <v>200</v>
       </c>
       <c r="B11" t="n">
-        <v>2.054</v>
+        <v>3.754</v>
       </c>
       <c r="C11" t="n">
-        <v>3.021</v>
+        <v>4.615</v>
       </c>
       <c r="D11" t="n">
-        <v>3.473</v>
+        <v>4.694</v>
       </c>
       <c r="E11" t="n">
-        <v>18.3</v>
+        <v>4.4</v>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>28.8</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2778.9</v>
+        <v>2865.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2822.7</v>
+        <v>2865.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2825.5</v>
+        <v>2875.9</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1179,31 +1179,31 @@
         <v>200</v>
       </c>
       <c r="B12" t="n">
-        <v>1.585</v>
+        <v>1.618</v>
       </c>
       <c r="C12" t="n">
-        <v>2.335</v>
+        <v>4.645</v>
       </c>
       <c r="D12" t="n">
-        <v>2.778</v>
+        <v>3.402</v>
       </c>
       <c r="E12" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>17.5</v>
+        <v>7.9</v>
       </c>
       <c r="G12" t="n">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2761.2</v>
+        <v>2868.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2767.1</v>
+        <v>2869.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2772.7</v>
+        <v>2872.5</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1214,31 +1214,31 @@
         <v>200</v>
       </c>
       <c r="B13" t="n">
-        <v>1.564</v>
+        <v>1.872</v>
       </c>
       <c r="C13" t="n">
-        <v>2.298</v>
+        <v>3.886</v>
       </c>
       <c r="D13" t="n">
-        <v>2.666</v>
+        <v>4.781</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>16.4</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2779.8</v>
+        <v>2887.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2779.3</v>
+        <v>2895.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2778.7</v>
+        <v>2892.7</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1249,31 +1249,31 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>1.72</v>
+        <v>1.486</v>
       </c>
       <c r="C14" t="n">
-        <v>2.617</v>
+        <v>4.388</v>
       </c>
       <c r="D14" t="n">
-        <v>3.132</v>
+        <v>3.299</v>
       </c>
       <c r="E14" t="n">
-        <v>16.3</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2764.6</v>
+        <v>2889.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2765.2</v>
+        <v>2886.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2763.9</v>
+        <v>2891.3</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1284,31 +1284,31 @@
         <v>500</v>
       </c>
       <c r="B15" t="n">
-        <v>1.661</v>
+        <v>1.713</v>
       </c>
       <c r="C15" t="n">
-        <v>2.482</v>
+        <v>2.934</v>
       </c>
       <c r="D15" t="n">
-        <v>4.148</v>
+        <v>4.726</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2746.5</v>
+        <v>2922.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2735.4</v>
+        <v>2923.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2736.6</v>
+        <v>2920.1</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1319,31 +1319,31 @@
         <v>500</v>
       </c>
       <c r="B16" t="n">
-        <v>1.687</v>
+        <v>1.368</v>
       </c>
       <c r="C16" t="n">
-        <v>2.562</v>
+        <v>3.762</v>
       </c>
       <c r="D16" t="n">
-        <v>4.062</v>
+        <v>3.924</v>
       </c>
       <c r="E16" t="n">
         <v>10.1</v>
       </c>
       <c r="F16" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2706.7</v>
+        <v>2898.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2709.2</v>
+        <v>2897.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2708.5</v>
+        <v>2900.5</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
